--- a/光伏配储项目/电价数据/2026/金源站.xlsx
+++ b/光伏配储项目/电价数据/2026/金源站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.52198</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7641699999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.58641</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5798300000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52071</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.53196</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43604</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44119</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49096</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.00739</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.01174</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.03449</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.10563</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.22364</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03106</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.12755</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.20936</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21494</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.22417</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20622</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.47548</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.51367</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73353</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.0801</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.9428500000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43725</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65998</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.82221</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43101</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.15669</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.73087</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.07621</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.23993</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6412100000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6926599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.25337</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.04131</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87317</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7589600000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51961</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48099</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47158</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42617</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71231</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.78057</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8747</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.92148</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51851</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50527</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5055299999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48761</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.9739099999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.81757</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.90088</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46886</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50754</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.24359</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.66625</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.87002</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8478300000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.78604</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.81763</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.99264</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.09628</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.46502</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5028899999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.80914</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.63271</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7726499999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.79089</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15887</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24744</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18958</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8550399999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20334</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10435</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25731</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03443</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08941</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98238</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90555</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9707899999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84377</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.9458300000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7758400000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.74918</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7689400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.78913</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33473</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51007</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48846</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49072</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42938</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44509</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47431</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43953</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.18694</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.01306</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.13374</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.14446</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.06365999999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.09308</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25088</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.7061499999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.05821</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.62397</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.6994600000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.51949</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.43184</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81091</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.65626</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.61863</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.51437</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.47558</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.18947</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.47954</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.55489</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.56514</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5056499999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.52716</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.2783</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61891</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46296</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50657</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60668</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5681900000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46015</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61375</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.6309400000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5619700000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7555599999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.63406</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.54883</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.46421</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.59878</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3421</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52739</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49381</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45015</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.23111</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.23913</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.62286</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.6217699999999999</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4598</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.52764</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60729</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47315</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49532</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.48883</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49936</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46391</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47517</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5694600000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.44121</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55474</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47249</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32115</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.17696</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.19913</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15643</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.07412000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.21228</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.17375</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.13931</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.01309</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00346</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27698</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.5036700000000001</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35217</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6678200000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22349</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05787</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.21836</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.00288</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07762999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07590000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33613</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31746</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45644</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18711</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86809</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.49636</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33087</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03293</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77299</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49317</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39991</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20702</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59776</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.73991</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87909</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58592</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88507</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63789</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86265</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87497</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4453</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.7090700000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.70941</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60073</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45761</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35454</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91975</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47068</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50678</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16114</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27235</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19905</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45137</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.60775</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89354</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47336</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16236</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7017899999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79267</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65274</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59405</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45227</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50266</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50787</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43586</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43594</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45672</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49635</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55736</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16151</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26175</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57564</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46782</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8541799999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47033</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.46635</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32646</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22541</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13253</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.13195</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13149</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25641</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13313</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24479</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13147</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25218</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1947</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11289</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.09268999999999999</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10917</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11631</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19163</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13063</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45724</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44895</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35114</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54695</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4744</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23453</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.5133300000000001</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.58331</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24309</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.5179900000000001</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36226</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.51179</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.52289</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.21605</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6852</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.25986</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43066</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.8442999999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24023</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>1.56178</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.61433</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7774</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.6234500000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.15456</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.62805</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.45716</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43937</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69474</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.77608</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.69609</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.58305</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51135</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34944</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3508</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6577799999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8006599999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34624</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.12564</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.18947</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.20881</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64177</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5998300000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5981000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.80787</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8313200000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48722</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36292</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.50146</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5284500000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.7156399999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.58061</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.51518</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.46124</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.51113</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45901</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.50344</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.49881</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5833200000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8837699999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.5052300000000001</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.45968</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52595</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.52735</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.73072</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.87863</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.96727</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.68303</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.84321</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.71954</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.56292</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.87127</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7727999999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62582</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67472</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4967200000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.49521</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48877</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48149</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42446</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46626</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46932</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.49405</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17997</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.20416</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.41024</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.37775</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.24175</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2238</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24425</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24257</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.15771</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24765</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18052</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22716</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23134</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35418</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26836</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01886</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00079</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14706</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02053</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01509</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04275</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04061</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04821</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02912</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0386</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01778</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03615</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20153</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26409</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32329</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6981799999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.59178</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24924</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62166</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.79803</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83989</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10455</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.18456</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.25536</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.22853</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00334</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.26003</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00276</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.27773</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.46866</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.44725</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.77391</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.73384</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7485000000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.30718</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97929</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7364700000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.81964</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7708700000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83829</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83646</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8408300000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93791</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.72894</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.76677</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7324299999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36021</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.59285</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.60415</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.55547</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47458</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.4621499999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7302999999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47913</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34041</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.56348</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7677200000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.54592</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.56224</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.45346</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47529</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48526</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8124</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5513899999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54153</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.58045</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83151</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7235900000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.56463</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.51096</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43009</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46177</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25182</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3699</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48023</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43547</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42742</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.66772</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.74349</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.70929</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.82582</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.59636</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.66565</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6047</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.9967699999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.8304400000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.37579</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.1783</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.08177</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.85603</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45663</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37419</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.19081</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.26964</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25818</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.10893</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.10562</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16438</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18647</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.24774</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.20682</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.2253</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.51489</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42353</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46876</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43982</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41452</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38189</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.04436</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.9732999999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.61781</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.66067</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.14013</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.57239</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8782000000000001</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.5757100000000001</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44505</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36884</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17479</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14451</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19682</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.09304999999999999</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.01924</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.08574</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.24246</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.16726</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.20853</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.11078</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.24603</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20784</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22518</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26264</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15432</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21469</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19682</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14389</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48156</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39188</v>
       </c>
     </row>
   </sheetData>
